--- a/SOSDB解析管理.xlsx
+++ b/SOSDB解析管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://b0aa600df9934664bf4b-my.sharepoint.com/personal/masaharu_itou_ab_east_ntt_co_jp/Documents/ドキュメント/GitHub/SOSDB_Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72339" documentId="8_{4F1CE34B-47BD-4B7F-91E2-EDB267A856C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F779B8D5-9E9D-48C3-83FD-02D0CB05BD33}"/>
+  <xr:revisionPtr revIDLastSave="103110" documentId="8_{4F1CE34B-47BD-4B7F-91E2-EDB267A856C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FA6C691-08F2-4E79-9F24-D5915DA31E33}"/>
   <bookViews>
-    <workbookView xWindow="975" yWindow="975" windowWidth="24000" windowHeight="12000" firstSheet="2" activeTab="5" xr2:uid="{6F7226F2-55B8-4AF5-95FC-B72D4BA47920}"/>
+    <workbookView xWindow="8370" yWindow="255" windowWidth="17955" windowHeight="14700" tabRatio="715" firstSheet="3" activeTab="5" xr2:uid="{6F7226F2-55B8-4AF5-95FC-B72D4BA47920}"/>
   </bookViews>
   <sheets>
     <sheet name="PathChartTree" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7169" uniqueCount="2251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7188" uniqueCount="2266">
   <si>
     <t>Module</t>
   </si>
@@ -6755,59 +6755,103 @@
     <t>　　│┴End If</t>
   </si>
   <si>
+    <t>　　□ Dim http As XMLHTTP60</t>
+  </si>
+  <si>
+    <t>　　〇 Set http = New XMLHTTP60</t>
+  </si>
+  <si>
+    <t>　　〇 http.send</t>
+  </si>
+  <si>
     <t>　　→ Exit Function</t>
   </si>
   <si>
-    <t>〇│Public Function GetResourceNameFromLocalDrive(strDrv As String) As String</t>
-  </si>
-  <si>
-    <t>　　□ Dim strBuf As String</t>
-  </si>
-  <si>
-    <t>　　□ Dim strDriveName As String</t>
-  </si>
-  <si>
-    <t>　　□ Dim lngLen As Long</t>
-  </si>
-  <si>
-    <t>　　〇 strDriveName = Left$(strDrv, 1) &amp; g_cnsCol</t>
-  </si>
-  <si>
-    <t>　　☆ On Error GoTo GetResourceNameFromLocalDrive_ERROR</t>
-  </si>
-  <si>
-    <t>　　〇 strBuf = String$(MAX_PATH + 1, vbNullChar)</t>
-  </si>
-  <si>
-    <t>　　〇 WNetGetConnection strDriveName, strBuf, MAX_PATH</t>
-  </si>
-  <si>
-    <t>　　〇 lngLen = InStr(1, strBuf, vbNullChar)</t>
-  </si>
-  <si>
-    <t>　　◆┐If lngLen &gt; 1 Then</t>
-  </si>
-  <si>
-    <t>　　│〇 GetResourceNameFromLocalDrive = Left$(strBuf, lngLen - 1)</t>
-  </si>
-  <si>
-    <t>　　├┐ELSE</t>
-  </si>
-  <si>
-    <t>　　│〇 GetResourceNameFromLocalDrive = strDriveName</t>
-  </si>
-  <si>
-    <t>　　☆ On Error GoTo 0</t>
-  </si>
-  <si>
-    <t>▼ GetResourceNameFromLocalDrive_ERROR:</t>
-  </si>
-  <si>
-    <t>　　〇 GetResourceNameFromLocalDrive = strDriveName</t>
-  </si>
-  <si>
-    <t>Procedure: modFileUtility.GetResourceNameFromLocalDrive</t>
-    <phoneticPr fontId="1"/>
+    <t>　　│→ GoTo CleanUp</t>
+  </si>
+  <si>
+    <t>▼ CleanUp:</t>
+  </si>
+  <si>
+    <t>　　☆ Resume CleanUp</t>
+  </si>
+  <si>
+    <t>　　☆ On Error GoTo ErrorHandler</t>
+  </si>
+  <si>
+    <t>▼ ErrorHandler:</t>
+  </si>
+  <si>
+    <t>Procedure: XmlSearch.DbtotalCount  [ 検索件数取得＜XmlSearch＞ ]</t>
+  </si>
+  <si>
+    <t>〇│Public Function DbtotalCount(ByVal apiUrl As String, ByVal apiKey As String) As Long</t>
+  </si>
+  <si>
+    <t>検索件数取得＜XmlSearch＞</t>
+  </si>
+  <si>
+    <t>　　□ Dim xmlDoc As DOMDocument60</t>
+  </si>
+  <si>
+    <t>　　□ Dim rootNode As IXMLDOMElement</t>
+  </si>
+  <si>
+    <t>　　□ Dim statusCode As Integer</t>
+  </si>
+  <si>
+    <t>　　〇 DbtotalCount = 0</t>
+  </si>
+  <si>
+    <t>　　〇 http.Open "GET", apiUrl, False</t>
+  </si>
+  <si>
+    <t>　　〇 http.setRequestHeader "X-Redmine-API-Key", apiKey</t>
+  </si>
+  <si>
+    <t>　　〇 statusCode = http.Status</t>
+  </si>
+  <si>
+    <t>　　◆ If statusCode = 1223 Then statusCode = 204</t>
+  </si>
+  <si>
+    <t>　　◆┐If statusCode &lt;&gt; 200 Then</t>
+  </si>
+  <si>
+    <t>　　│〇 MsgBox "接続失敗: " &amp; statusCode, vbCritical</t>
+  </si>
+  <si>
+    <t>　　◆┐If Len(http.responseText) = 0 Then</t>
+  </si>
+  <si>
+    <t>　　│〇 MsgBox "データなし（204）", vbInformation</t>
+  </si>
+  <si>
+    <t>　　〇 Set xmlDoc = New DOMDocument60</t>
+  </si>
+  <si>
+    <t>　　〇 xmlDoc.LoadXML http.responseText</t>
+  </si>
+  <si>
+    <t>　　◆┐If xmlDoc.parseError.ErrorCode &lt;&gt; 0 Then</t>
+  </si>
+  <si>
+    <t>　　│〇 MsgBox "XML解析失敗: " &amp; xmlDoc.parseError.reason, vbCritical</t>
+  </si>
+  <si>
+    <t>　　〇 Set rootNode = xmlDoc.DocumentElement</t>
+  </si>
+  <si>
+    <t>　　〇 DbtotalCount = CLng(rootNode.getAttribute("total_count"))</t>
+  </si>
+  <si>
+    <t>　　◎ Call ReleaseHttpObjects(http, xmlDoc, rootNode)</t>
+  </si>
+  <si>
+    <t>通信オブジェクト解放＜XmlSearch＞</t>
+  </si>
+  <si>
+    <t>　　〇 MsgBox "エラー: " &amp; Err.Description, vbCritical</t>
   </si>
 </sst>
 </file>
@@ -6934,35 +6978,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -12553,6 +12569,10 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -36115,16 +36135,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E23A63-1614-48FF-BDCA-38E652C8DFC4}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="150.625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="60.625" customWidth="1"/>
+    <col min="1" max="1" width="120.625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
-        <v>2250</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -36142,7 +36162,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>2234</v>
+        <v>2243</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2244</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -36152,27 +36175,27 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>2236</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>2237</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>2238</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
-        <v>2239</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
@@ -36182,61 +36205,149 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
-        <v>2241</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>2242</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>2243</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
-        <v>2246</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
-        <v>2232</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
-        <v>2247</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
-        <v>2233</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
-        <v>2248</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
-        <v>2249</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" s="8" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" s="8" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" s="8" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" s="8" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" s="8" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" s="8" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" s="8" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" s="8" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" s="8" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" s="8" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" s="8" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" s="8" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" s="8" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" s="8" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" s="8" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" s="8" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" s="8" t="s">
         <v>2231</v>
       </c>
     </row>

--- a/SOSDB解析管理.xlsx
+++ b/SOSDB解析管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://b0aa600df9934664bf4b-my.sharepoint.com/personal/masaharu_itou_ab_east_ntt_co_jp/Documents/ドキュメント/GitHub/SOSDB_Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103110" documentId="8_{4F1CE34B-47BD-4B7F-91E2-EDB267A856C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FA6C691-08F2-4E79-9F24-D5915DA31E33}"/>
+  <xr:revisionPtr revIDLastSave="103184" documentId="8_{4F1CE34B-47BD-4B7F-91E2-EDB267A856C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E365F73D-350C-47F4-A4B6-805DEC356547}"/>
   <bookViews>
-    <workbookView xWindow="8370" yWindow="255" windowWidth="17955" windowHeight="14700" tabRatio="715" firstSheet="3" activeTab="5" xr2:uid="{6F7226F2-55B8-4AF5-95FC-B72D4BA47920}"/>
+    <workbookView xWindow="1995" yWindow="1020" windowWidth="24000" windowHeight="12000" tabRatio="715" firstSheet="3" activeTab="5" xr2:uid="{6F7226F2-55B8-4AF5-95FC-B72D4BA47920}"/>
   </bookViews>
   <sheets>
     <sheet name="PathChartTree" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7188" uniqueCount="2266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7176" uniqueCount="2257">
   <si>
     <t>Module</t>
   </si>
@@ -6749,109 +6749,82 @@
     <t>┴└┐</t>
   </si>
   <si>
-    <t>　　┴End Function</t>
-  </si>
-  <si>
     <t>　　│┴End If</t>
   </si>
   <si>
-    <t>　　□ Dim http As XMLHTTP60</t>
-  </si>
-  <si>
-    <t>　　〇 Set http = New XMLHTTP60</t>
-  </si>
-  <si>
-    <t>　　〇 http.send</t>
-  </si>
-  <si>
-    <t>　　→ Exit Function</t>
-  </si>
-  <si>
-    <t>　　│→ GoTo CleanUp</t>
-  </si>
-  <si>
-    <t>▼ CleanUp:</t>
-  </si>
-  <si>
-    <t>　　☆ Resume CleanUp</t>
-  </si>
-  <si>
     <t>　　☆ On Error GoTo ErrorHandler</t>
   </si>
   <si>
     <t>▼ ErrorHandler:</t>
   </si>
   <si>
-    <t>Procedure: XmlSearch.DbtotalCount  [ 検索件数取得＜XmlSearch＞ ]</t>
-  </si>
-  <si>
-    <t>〇│Public Function DbtotalCount(ByVal apiUrl As String, ByVal apiKey As String) As Long</t>
-  </si>
-  <si>
-    <t>検索件数取得＜XmlSearch＞</t>
-  </si>
-  <si>
-    <t>　　□ Dim xmlDoc As DOMDocument60</t>
-  </si>
-  <si>
-    <t>　　□ Dim rootNode As IXMLDOMElement</t>
-  </si>
-  <si>
-    <t>　　□ Dim statusCode As Integer</t>
-  </si>
-  <si>
-    <t>　　〇 DbtotalCount = 0</t>
-  </si>
-  <si>
-    <t>　　〇 http.Open "GET", apiUrl, False</t>
-  </si>
-  <si>
-    <t>　　〇 http.setRequestHeader "X-Redmine-API-Key", apiKey</t>
-  </si>
-  <si>
-    <t>　　〇 statusCode = http.Status</t>
-  </si>
-  <si>
-    <t>　　◆ If statusCode = 1223 Then statusCode = 204</t>
-  </si>
-  <si>
-    <t>　　◆┐If statusCode &lt;&gt; 200 Then</t>
-  </si>
-  <si>
-    <t>　　│〇 MsgBox "接続失敗: " &amp; statusCode, vbCritical</t>
-  </si>
-  <si>
-    <t>　　◆┐If Len(http.responseText) = 0 Then</t>
-  </si>
-  <si>
-    <t>　　│〇 MsgBox "データなし（204）", vbInformation</t>
-  </si>
-  <si>
-    <t>　　〇 Set xmlDoc = New DOMDocument60</t>
-  </si>
-  <si>
-    <t>　　〇 xmlDoc.LoadXML http.responseText</t>
-  </si>
-  <si>
-    <t>　　◆┐If xmlDoc.parseError.ErrorCode &lt;&gt; 0 Then</t>
-  </si>
-  <si>
-    <t>　　│〇 MsgBox "XML解析失敗: " &amp; xmlDoc.parseError.reason, vbCritical</t>
-  </si>
-  <si>
-    <t>　　〇 Set rootNode = xmlDoc.DocumentElement</t>
-  </si>
-  <si>
-    <t>　　〇 DbtotalCount = CLng(rootNode.getAttribute("total_count"))</t>
-  </si>
-  <si>
-    <t>　　◎ Call ReleaseHttpObjects(http, xmlDoc, rootNode)</t>
-  </si>
-  <si>
-    <t>通信オブジェクト解放＜XmlSearch＞</t>
-  </si>
-  <si>
-    <t>　　〇 MsgBox "エラー: " &amp; Err.Description, vbCritical</t>
+    <t>Procedure: XmlSearch.DbSearch  [ Redmine検索実行＜XmlSearch＞ ]</t>
+  </si>
+  <si>
+    <t>〇│Sub DbSearch(SearchKey As String)</t>
+  </si>
+  <si>
+    <t>Redmine検索実行＜XmlSearch＞</t>
+  </si>
+  <si>
+    <t>　　□ Dim Author_Name As String</t>
+  </si>
+  <si>
+    <t>　　□ Dim apiKey As String</t>
+  </si>
+  <si>
+    <t>　　□ Dim SearchUrl As String</t>
+  </si>
+  <si>
+    <t>　　□ Dim url As String</t>
+  </si>
+  <si>
+    <t>　　□ Dim ResultMsg As String</t>
+  </si>
+  <si>
+    <t>　　〇 Author_Name = Range(TANTOU_NAME_RANG).Value</t>
+  </si>
+  <si>
+    <t>　　◎ apiKey = GetApiKey(Author_Name)</t>
+  </si>
+  <si>
+    <t>APIキー取得＜modIssueMapper＞</t>
+  </si>
+  <si>
+    <t>　　◆┐If (apiKey = "") Then</t>
+  </si>
+  <si>
+    <t>　　│〇 apiKey = Read_API_Key</t>
+  </si>
+  <si>
+    <t>　　◆┐If apiKey = "" Then</t>
+  </si>
+  <si>
+    <t>　　│〇 MsgBox "APIキーの取得に失敗しました。", vbCritical</t>
+  </si>
+  <si>
+    <t>　　│→ Exit Sub</t>
+  </si>
+  <si>
+    <t>　　◎ SearchUrl = MakeSearchUrl(SearchKey)</t>
+  </si>
+  <si>
+    <t>検索URL生成＜XmlSearch＞</t>
+  </si>
+  <si>
+    <t>　　◎ Call ExportRedmineIDsToCSV(SearchKey, SearchUrl, apiKey)</t>
+  </si>
+  <si>
+    <t>検索結果CSV生成＜XmlSearch＞</t>
+  </si>
+  <si>
+    <t>　　→ Exit Sub</t>
+  </si>
+  <si>
+    <t>　　〇 MsgBox "検索中にエラーが発生しました。" &amp; vbCrLf &amp;  "エラー番号: " &amp; Err.Number &amp; vbCrLf &amp;  "内容: " &amp; Err.Description, vbCritical, "DbtotalCount"</t>
+  </si>
+  <si>
+    <t>　　┴End Sub</t>
   </si>
 </sst>
 </file>
@@ -12569,10 +12542,6 @@
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -36135,7 +36104,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E23A63-1614-48FF-BDCA-38E652C8DFC4}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="120.625" style="8" customWidth="1"/>
@@ -36144,7 +36113,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
-        <v>2242</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -36162,10 +36131,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>2243</v>
+        <v>2235</v>
       </c>
       <c r="B4" t="s">
-        <v>2244</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -36175,180 +36144,116 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
-        <v>2233</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>2245</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>2246</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>2247</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
-        <v>2248</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
-        <v>2240</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
-        <v>2234</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>2249</v>
+        <v>2243</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2244</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>2250</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
-        <v>2235</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="8" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" s="8" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="8" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="8" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="8" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B21" t="s">
         <v>2251</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" s="8" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="8" t="s">
         <v>2252</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
+      <c r="B22" t="s">
         <v>2253</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" s="8" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="8" t="s">
         <v>2254</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" s="8" t="s">
-        <v>2232</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" s="8" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="8" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A25" s="8" t="s">
         <v>2255</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" s="8" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="8" t="s">
         <v>2256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A24" s="8" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" s="8" t="s">
-        <v>2232</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A26" s="8" t="s">
-        <v>2257</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A27" s="8" t="s">
-        <v>2258</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" s="8" t="s">
-        <v>2259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A29" s="8" t="s">
-        <v>2260</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A30" s="8" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A31" s="8" t="s">
-        <v>2232</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A32" s="8" t="s">
-        <v>2261</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33" s="8" t="s">
-        <v>2262</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34" s="8" t="s">
-        <v>2238</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" s="8" t="s">
-        <v>2263</v>
-      </c>
-      <c r="B35" t="s">
-        <v>2264</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" s="8" t="s">
-        <v>2236</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" s="8" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" s="8" t="s">
-        <v>2265</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39" s="8" t="s">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40" s="8" t="s">
-        <v>2231</v>
       </c>
     </row>
   </sheetData>
